--- a/notebooks/CalSim3GroundWaterDataExtractionInitFile_v1.xlsx
+++ b/notebooks/CalSim3GroundWaterDataExtractionInitFile_v1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0493170D-B48B-463C-9B0A-19066E381E50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{262A0231-819A-456B-BDEC-11C92112BD7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,6 +11,7 @@
     <sheet name="Init" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -231,25 +232,25 @@
     <t>O475</t>
   </si>
   <si>
-    <t>A36</t>
-  </si>
-  <si>
-    <t>B36</t>
-  </si>
-  <si>
-    <t>C36</t>
-  </si>
-  <si>
-    <t>G36</t>
-  </si>
-  <si>
-    <t>H36</t>
-  </si>
-  <si>
-    <t>I36</t>
-  </si>
-  <si>
-    <t>J36</t>
+    <t>A39</t>
+  </si>
+  <si>
+    <t>B39</t>
+  </si>
+  <si>
+    <t>C39</t>
+  </si>
+  <si>
+    <t>G39</t>
+  </si>
+  <si>
+    <t>H39</t>
+  </si>
+  <si>
+    <t>I39</t>
+  </si>
+  <si>
+    <t>J39</t>
   </si>
 </sst>
 </file>

--- a/notebooks/CalSim3GroundWaterDataExtractionInitFile_v1.xlsx
+++ b/notebooks/CalSim3GroundWaterDataExtractionInitFile_v1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{262A0231-819A-456B-BDEC-11C92112BD7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98CF4791-66E4-4955-B9C6-D6E88889A2E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -232,25 +232,25 @@
     <t>O475</t>
   </si>
   <si>
-    <t>A39</t>
-  </si>
-  <si>
-    <t>B39</t>
-  </si>
-  <si>
-    <t>C39</t>
-  </si>
-  <si>
-    <t>G39</t>
-  </si>
-  <si>
-    <t>H39</t>
-  </si>
-  <si>
-    <t>I39</t>
-  </si>
-  <si>
-    <t>J39</t>
+    <t>B40</t>
+  </si>
+  <si>
+    <t>C40</t>
+  </si>
+  <si>
+    <t>G40</t>
+  </si>
+  <si>
+    <t>H40</t>
+  </si>
+  <si>
+    <t>I40</t>
+  </si>
+  <si>
+    <t>J40</t>
+  </si>
+  <si>
+    <t>A40</t>
   </si>
 </sst>
 </file>
@@ -644,7 +644,7 @@
         <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -659,7 +659,7 @@
         <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E6" s="2"/>
     </row>
@@ -674,7 +674,7 @@
         <v>19</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E7" s="2"/>
     </row>
@@ -689,7 +689,7 @@
         <v>20</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E8" s="2"/>
     </row>
@@ -704,7 +704,7 @@
         <v>21</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E9" s="2"/>
     </row>
@@ -719,7 +719,7 @@
         <v>22</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E10" s="2"/>
     </row>
@@ -734,7 +734,7 @@
         <v>35</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E11" s="2"/>
     </row>

--- a/notebooks/CalSim3GroundWaterDataExtractionInitFile_v1.xlsx
+++ b/notebooks/CalSim3GroundWaterDataExtractionInitFile_v1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98CF4791-66E4-4955-B9C6-D6E88889A2E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AC915A4-3BEA-4089-92B0-AE21CC4B603C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -226,31 +226,31 @@
     <t>SV Dss path names</t>
   </si>
   <si>
-    <t>E258</t>
-  </si>
-  <si>
     <t>O475</t>
   </si>
   <si>
-    <t>B40</t>
-  </si>
-  <si>
-    <t>C40</t>
-  </si>
-  <si>
-    <t>G40</t>
-  </si>
-  <si>
-    <t>H40</t>
-  </si>
-  <si>
-    <t>I40</t>
-  </si>
-  <si>
-    <t>J40</t>
-  </si>
-  <si>
-    <t>A40</t>
+    <t>E261</t>
+  </si>
+  <si>
+    <t>A46</t>
+  </si>
+  <si>
+    <t>B46</t>
+  </si>
+  <si>
+    <t>C46</t>
+  </si>
+  <si>
+    <t>G46</t>
+  </si>
+  <si>
+    <t>H46</t>
+  </si>
+  <si>
+    <t>I46</t>
+  </si>
+  <si>
+    <t>J46</t>
   </si>
 </sst>
 </file>
@@ -644,7 +644,7 @@
         <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -659,7 +659,7 @@
         <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E6" s="2"/>
     </row>
@@ -674,7 +674,7 @@
         <v>19</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E7" s="2"/>
     </row>
@@ -689,7 +689,7 @@
         <v>20</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E8" s="2"/>
     </row>
@@ -704,7 +704,7 @@
         <v>21</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E9" s="2"/>
     </row>
@@ -719,7 +719,7 @@
         <v>22</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E10" s="2"/>
     </row>
@@ -734,7 +734,7 @@
         <v>35</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E11" s="2"/>
     </row>
@@ -773,7 +773,7 @@
         <v>25</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -835,7 +835,7 @@
         <v>43</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">

--- a/notebooks/CalSim3GroundWaterDataExtractionInitFile_v1.xlsx
+++ b/notebooks/CalSim3GroundWaterDataExtractionInitFile_v1.xlsx
@@ -3,15 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AC915A4-3BEA-4089-92B0-AE21CC4B603C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4FC06BD-C6D3-4D91-88A3-F765E5FC6263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-2700" yWindow="-21720" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Init" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -229,9 +228,6 @@
     <t>O475</t>
   </si>
   <si>
-    <t>E261</t>
-  </si>
-  <si>
     <t>A46</t>
   </si>
   <si>
@@ -251,6 +247,9 @@
   </si>
   <si>
     <t>J46</t>
+  </si>
+  <si>
+    <t>E265</t>
   </si>
 </sst>
 </file>
@@ -644,7 +643,7 @@
         <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -659,7 +658,7 @@
         <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E6" s="2"/>
     </row>
@@ -674,7 +673,7 @@
         <v>19</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E7" s="2"/>
     </row>
@@ -689,7 +688,7 @@
         <v>20</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E8" s="2"/>
     </row>
@@ -704,7 +703,7 @@
         <v>21</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E9" s="2"/>
     </row>
@@ -719,7 +718,7 @@
         <v>22</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E10" s="2"/>
     </row>
@@ -734,7 +733,7 @@
         <v>35</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E11" s="2"/>
     </row>
@@ -773,7 +772,7 @@
         <v>25</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">

--- a/notebooks/CalSim3GroundWaterDataExtractionInitFile_v1.xlsx
+++ b/notebooks/CalSim3GroundWaterDataExtractionInitFile_v1.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4FC06BD-C6D3-4D91-88A3-F765E5FC6263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5130821E-3D43-4E1F-BF6C-47B18CAD94B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2700" yWindow="-21720" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3576" yWindow="3408" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Init" sheetId="1" r:id="rId1"/>
@@ -249,7 +249,7 @@
     <t>J46</t>
   </si>
   <si>
-    <t>E265</t>
+    <t>E266</t>
   </si>
 </sst>
 </file>

--- a/notebooks/CalSim3GroundWaterDataExtractionInitFile_v1.xlsx
+++ b/notebooks/CalSim3GroundWaterDataExtractionInitFile_v1.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5130821E-3D43-4E1F-BF6C-47B18CAD94B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1530DFB8-3022-4DB9-88CA-1F79B74FBE16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3576" yWindow="3408" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Init" sheetId="1" r:id="rId1"/>
@@ -228,28 +228,28 @@
     <t>O475</t>
   </si>
   <si>
-    <t>A46</t>
-  </si>
-  <si>
-    <t>B46</t>
-  </si>
-  <si>
-    <t>C46</t>
-  </si>
-  <si>
-    <t>G46</t>
-  </si>
-  <si>
-    <t>H46</t>
-  </si>
-  <si>
-    <t>I46</t>
-  </si>
-  <si>
-    <t>J46</t>
-  </si>
-  <si>
     <t>E266</t>
+  </si>
+  <si>
+    <t>A49</t>
+  </si>
+  <si>
+    <t>B49</t>
+  </si>
+  <si>
+    <t>C49</t>
+  </si>
+  <si>
+    <t>G49</t>
+  </si>
+  <si>
+    <t>H49</t>
+  </si>
+  <si>
+    <t>I49</t>
+  </si>
+  <si>
+    <t>J49</t>
   </si>
 </sst>
 </file>
@@ -643,7 +643,7 @@
         <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -658,7 +658,7 @@
         <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E6" s="2"/>
     </row>
@@ -673,7 +673,7 @@
         <v>19</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E7" s="2"/>
     </row>
@@ -688,7 +688,7 @@
         <v>20</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E8" s="2"/>
     </row>
@@ -703,7 +703,7 @@
         <v>21</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E9" s="2"/>
     </row>
@@ -718,7 +718,7 @@
         <v>22</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E10" s="2"/>
     </row>
@@ -733,7 +733,7 @@
         <v>35</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E11" s="2"/>
     </row>
@@ -772,7 +772,7 @@
         <v>25</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">

--- a/notebooks/CalSim3GroundWaterDataExtractionInitFile_v1.xlsx
+++ b/notebooks/CalSim3GroundWaterDataExtractionInitFile_v1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1530DFB8-3022-4DB9-88CA-1F79B74FBE16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F1C3EF1-90F3-4CBC-8F34-F22BAAB91097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -231,25 +231,25 @@
     <t>E266</t>
   </si>
   <si>
-    <t>A49</t>
-  </si>
-  <si>
-    <t>B49</t>
-  </si>
-  <si>
-    <t>C49</t>
-  </si>
-  <si>
-    <t>G49</t>
-  </si>
-  <si>
-    <t>H49</t>
-  </si>
-  <si>
-    <t>I49</t>
-  </si>
-  <si>
-    <t>J49</t>
+    <t>A25</t>
+  </si>
+  <si>
+    <t>B25</t>
+  </si>
+  <si>
+    <t>C25</t>
+  </si>
+  <si>
+    <t>G25</t>
+  </si>
+  <si>
+    <t>H25</t>
+  </si>
+  <si>
+    <t>I25</t>
+  </si>
+  <si>
+    <t>J25</t>
   </si>
 </sst>
 </file>

--- a/notebooks/CalSim3GroundWaterDataExtractionInitFile_v1.xlsx
+++ b/notebooks/CalSim3GroundWaterDataExtractionInitFile_v1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F1C3EF1-90F3-4CBC-8F34-F22BAAB91097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96085474-AFFF-4CE1-96C6-9795E96A376A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -231,25 +231,25 @@
     <t>E266</t>
   </si>
   <si>
-    <t>A25</t>
-  </si>
-  <si>
-    <t>B25</t>
-  </si>
-  <si>
-    <t>C25</t>
-  </si>
-  <si>
-    <t>G25</t>
-  </si>
-  <si>
-    <t>H25</t>
-  </si>
-  <si>
-    <t>I25</t>
-  </si>
-  <si>
-    <t>J25</t>
+    <t>A26</t>
+  </si>
+  <si>
+    <t>B26</t>
+  </si>
+  <si>
+    <t>C26</t>
+  </si>
+  <si>
+    <t>G26</t>
+  </si>
+  <si>
+    <t>H26</t>
+  </si>
+  <si>
+    <t>I26</t>
+  </si>
+  <si>
+    <t>J26</t>
   </si>
 </sst>
 </file>
